--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA506D96-49CB-4C13-BA28-ACBBE8A2DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CF789-70E7-4DC0-88EA-1AD99B90A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="7650" yWindow="9600" windowWidth="23010" windowHeight="13770" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Source:</t>
   </si>
@@ -124,6 +124,36 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the US, many coal plants are subject to rules requiring them </t>
+  </si>
+  <si>
+    <t>to retrofit to meet enviromental guidelines. This requires</t>
+  </si>
+  <si>
+    <t>a one time investment decision for plant owners. Because we don't</t>
+  </si>
+  <si>
+    <t>track individual plants in the model, we calibrate the share of forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costs that must be recovered to represent the additional revenue that is needed to </t>
+  </si>
+  <si>
+    <t>save and pay for these one time investments and apply this across the distribution</t>
+  </si>
+  <si>
+    <t>of plant types. Calibration is done by comparing model results against other sources,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">including Rhodium's ClimateDeck and EIA's Annual Energy Outlook and Electric </t>
+  </si>
+  <si>
+    <t>Power Monthly.</t>
   </si>
 </sst>
 </file>
@@ -197,9 +227,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -237,7 +267,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -343,7 +373,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,7 +515,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -493,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -507,6 +537,54 @@
       </c>
       <c r="B3" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -538,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CF789-70E7-4DC0-88EA-1AD99B90A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6456AFA-3211-4C4C-B571-DE05B7AD9815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="9600" windowWidth="23010" windowHeight="13770" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="24165" windowHeight="13365" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoFCtMbCtPR " sheetId="2" r:id="rId2"/>
+    <sheet name="SoFCtMbCtPR" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -205,10 +205,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,7 +598,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
@@ -615,7 +616,7 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>2.5</v>
       </c>
     </row>
@@ -623,7 +624,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
     </row>
@@ -631,7 +632,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
     </row>
@@ -639,7 +640,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -647,7 +648,7 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -655,7 +656,7 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -663,7 +664,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -671,7 +672,7 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -679,7 +680,7 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -687,7 +688,7 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -695,7 +696,7 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>1</v>
       </c>
     </row>
@@ -703,7 +704,7 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>1</v>
       </c>
     </row>
@@ -711,7 +712,7 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>1</v>
       </c>
     </row>
@@ -719,7 +720,7 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>1</v>
       </c>
     </row>
@@ -727,7 +728,7 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>1</v>
       </c>
     </row>
@@ -735,7 +736,7 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -743,7 +744,7 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>1</v>
       </c>
     </row>
@@ -751,7 +752,7 @@
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>1</v>
       </c>
     </row>
@@ -759,7 +760,7 @@
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -767,7 +768,7 @@
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>1</v>
       </c>
     </row>
@@ -775,7 +776,7 @@
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>1</v>
       </c>
     </row>
@@ -783,7 +784,7 @@
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>1</v>
       </c>
     </row>
@@ -791,7 +792,7 @@
       <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="3">
         <v>1</v>
       </c>
     </row>
@@ -799,9 +800,12 @@
       <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
